--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182732</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182701</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182726</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182670</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182692</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182668</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182674</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182730</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2201,6 +2271,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182698</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2308,6 +2383,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182694</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2415,6 +2495,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182672</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182678</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2629,6 +2719,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182684</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2736,6 +2831,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182688</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2843,6 +2943,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182703</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2950,6 +3055,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182713</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3057,6 +3167,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182676</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3164,6 +3279,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182680</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3271,6 +3391,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182690</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3378,6 +3503,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182696</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3485,8 +3615,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135182728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92409</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92411</v>
+        <v>92417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92417</v>
+        <v>92418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92418</v>
+        <v>92424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92424</v>
+        <v>92431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135182670</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135182692</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99218</v>
+        <v>99231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 29197-2026 artfynd.xlsx
+++ b/artfynd/A 29197-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135182739</v>
       </c>
       <c r="B2" t="n">
-        <v>92431</v>
+        <v>92432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135182732</v>
       </c>
       <c r="B3" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135182701</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135182705</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135182707</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135182709</v>
       </c>
       <c r="B7" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135182711</v>
       </c>
       <c r="B8" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135182726</v>
       </c>
       <c r="B9" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>135182668</v>
       </c>
       <c r="B12" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>135182674</v>
       </c>
       <c r="B13" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>135182730</v>
       </c>
       <c r="B14" t="n">
-        <v>99231</v>
+        <v>99232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135182698</v>
       </c>
       <c r="B15" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>135182694</v>
       </c>
       <c r="B16" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>135182672</v>
       </c>
       <c r="B17" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135182678</v>
       </c>
       <c r="B18" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>135182684</v>
       </c>
       <c r="B19" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>135182688</v>
       </c>
       <c r="B20" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>135182703</v>
       </c>
       <c r="B21" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>135182713</v>
       </c>
       <c r="B22" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>135182676</v>
       </c>
       <c r="B23" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>135182680</v>
       </c>
       <c r="B24" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>135182690</v>
       </c>
       <c r="B25" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>135182696</v>
       </c>
       <c r="B26" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>135182728</v>
       </c>
       <c r="B27" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
